--- a/config/bumen.xlsx
+++ b/config/bumen.xlsx
@@ -2084,7 +2084,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2104,61 +2104,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2767,7 +2716,7 @@
       <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -2781,13 +2730,13 @@
       <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2798,7 +2747,7 @@
       <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2812,7 +2761,7 @@
       <c r="C9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2823,10 +2772,10 @@
       <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2837,7 +2786,7 @@
       <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2851,7 +2800,7 @@
       <c r="C12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2862,10 +2811,10 @@
       <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2876,7 +2825,7 @@
       <c r="B14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="4" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2890,7 +2839,7 @@
       <c r="C15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="4" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2901,10 +2850,10 @@
       <c r="B16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="4" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2949,7 +2898,7 @@
       <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E20" s="4" t="s">
@@ -2963,7 +2912,7 @@
       <c r="B21" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="4" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2977,7 +2926,7 @@
       <c r="C22" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="4" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2988,10 +2937,10 @@
       <c r="B23" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="4" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3002,7 +2951,7 @@
       <c r="B24" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="4" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3016,7 +2965,7 @@
       <c r="C25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="4" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3027,10 +2976,10 @@
       <c r="B26" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="4" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3041,7 +2990,7 @@
       <c r="B27" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3055,7 +3004,7 @@
       <c r="C28" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3066,10 +3015,10 @@
       <c r="B29" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3089,7 +3038,7 @@
       <c r="B31" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="5" t="s">
         <v>75</v>
       </c>
     </row>
@@ -3103,7 +3052,7 @@
       <c r="C32" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="5" t="s">
         <v>75</v>
       </c>
     </row>
@@ -3114,10 +3063,10 @@
       <c r="B33" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="5" t="s">
         <v>75</v>
       </c>
     </row>
@@ -3128,10 +3077,10 @@
       <c r="B34" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="4" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3142,10 +3091,10 @@
       <c r="B35" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="4" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3156,7 +3105,7 @@
       <c r="B36" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="4" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3170,7 +3119,7 @@
       <c r="C37" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="4" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3181,10 +3130,10 @@
       <c r="B38" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="4" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3195,7 +3144,7 @@
       <c r="B39" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="5" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3209,7 +3158,7 @@
       <c r="C40" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="5" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3220,10 +3169,10 @@
       <c r="B41" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E41" s="12" t="s">
+      <c r="E41" s="5" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3234,13 +3183,13 @@
       <c r="B42" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="5" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3251,7 +3200,7 @@
       <c r="B43" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="4" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3265,7 +3214,7 @@
       <c r="C44" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="4" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3276,10 +3225,10 @@
       <c r="B45" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="4" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3290,7 +3239,7 @@
       <c r="B46" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C46" s="10"/>
+      <c r="C46" s="2"/>
     </row>
     <row r="47" s="1" customFormat="1" ht="12.5" spans="1:5">
       <c r="A47" s="1" t="s">
@@ -3299,13 +3248,13 @@
       <c r="B47" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="14" t="s">
+      <c r="D47" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="4" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3388,7 +3337,7 @@
       <c r="B56" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="5" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3402,7 +3351,7 @@
       <c r="C57" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="5" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3416,7 +3365,7 @@
       <c r="C58" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E58" s="12" t="s">
+      <c r="E58" s="5" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3424,10 +3373,10 @@
       <c r="A59" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C59" s="4" t="s">
         <v>140</v>
       </c>
       <c r="D59" s="1" t="s">
@@ -3438,13 +3387,13 @@
       <c r="A60" s="1">
         <v>10030704</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B60" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E60" s="15" t="s">
+      <c r="E60" s="6" t="s">
         <v>144</v>
       </c>
     </row>
@@ -3596,37 +3545,37 @@
       </c>
     </row>
     <row r="76" s="1" customFormat="1" ht="13" spans="1:5">
-      <c r="A76" s="17" t="s">
+      <c r="A76" s="2" t="s">
         <v>175</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="5" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" ht="13" spans="1:5">
-      <c r="A77" s="17" t="s">
+      <c r="A77" s="2" t="s">
         <v>178</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C77" s="2"/>
-      <c r="D77" s="6" t="s">
+      <c r="D77" s="5" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" ht="13" spans="1:5">
-      <c r="A78" s="17">
+      <c r="A78" s="2">
         <v>100802</v>
       </c>
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="6" t="s">
         <v>180</v>
       </c>
       <c r="C78" s="2"/>
-      <c r="E78" s="6" t="s">
+      <c r="E78" s="5" t="s">
         <v>177</v>
       </c>
     </row>
@@ -3646,13 +3595,13 @@
       <c r="B80" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C80" s="18" t="s">
+      <c r="C80" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="D80" s="18" t="s">
+      <c r="D80" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E80" s="18" t="s">
+      <c r="E80" s="5" t="s">
         <v>184</v>
       </c>
     </row>
@@ -3672,13 +3621,13 @@
       <c r="B82" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C82" s="19" t="s">
+      <c r="C82" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="D82" s="19" t="s">
+      <c r="D82" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E82" s="19" t="s">
+      <c r="E82" s="4" t="s">
         <v>188</v>
       </c>
     </row>
@@ -3698,7 +3647,7 @@
       <c r="B84" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C84" s="20" t="s">
+      <c r="C84" s="4" t="s">
         <v>192</v>
       </c>
     </row>
@@ -3710,7 +3659,7 @@
         <v>194</v>
       </c>
       <c r="C85" s="2"/>
-      <c r="D85" s="20" t="s">
+      <c r="D85" s="4" t="s">
         <v>192</v>
       </c>
     </row>
@@ -3722,7 +3671,7 @@
         <v>196</v>
       </c>
       <c r="C86" s="2"/>
-      <c r="E86" s="20" t="s">
+      <c r="E86" s="4" t="s">
         <v>192</v>
       </c>
     </row>
@@ -3733,13 +3682,10 @@
       <c r="B87" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C87" s="19" t="s">
+      <c r="C87" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="D87" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="E87" s="19" t="s">
+      <c r="E87" s="4" t="s">
         <v>198</v>
       </c>
     </row>
@@ -3751,7 +3697,9 @@
         <v>200</v>
       </c>
       <c r="C88" s="2"/>
-      <c r="D88" s="19"/>
+      <c r="D88" s="4" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="89" s="1" customFormat="1" ht="12.5" spans="1:5">
       <c r="A89" s="1" t="s">
@@ -3785,7 +3733,7 @@
       <c r="B91" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E91" s="4" t="s">
@@ -3799,7 +3747,7 @@
       <c r="B92" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C92" s="9" t="s">
+      <c r="C92" s="4" t="s">
         <v>208</v>
       </c>
     </row>
@@ -3813,7 +3761,7 @@
       <c r="C93" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D93" s="9" t="s">
+      <c r="D93" s="4" t="s">
         <v>208</v>
       </c>
     </row>
@@ -3824,10 +3772,10 @@
       <c r="B94" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E94" s="9" t="s">
+      <c r="E94" s="4" t="s">
         <v>208</v>
       </c>
     </row>
@@ -3838,7 +3786,7 @@
       <c r="B95" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C95" s="9" t="s">
+      <c r="C95" s="4" t="s">
         <v>214</v>
       </c>
     </row>
@@ -3852,7 +3800,7 @@
       <c r="C96" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D96" s="9" t="s">
+      <c r="D96" s="4" t="s">
         <v>214</v>
       </c>
     </row>
@@ -3863,10 +3811,10 @@
       <c r="B97" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C97" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E97" s="9" t="s">
+      <c r="E97" s="4" t="s">
         <v>214</v>
       </c>
     </row>
@@ -3877,7 +3825,7 @@
       <c r="B98" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C98" s="9" t="s">
+      <c r="C98" s="4" t="s">
         <v>220</v>
       </c>
     </row>
@@ -3891,7 +3839,7 @@
       <c r="C99" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D99" s="9" t="s">
+      <c r="D99" s="4" t="s">
         <v>220</v>
       </c>
     </row>
@@ -3902,10 +3850,10 @@
       <c r="B100" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C100" s="11" t="s">
+      <c r="C100" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E100" s="9" t="s">
+      <c r="E100" s="4" t="s">
         <v>220</v>
       </c>
     </row>
@@ -3916,13 +3864,13 @@
       <c r="B101" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C101" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="D101" s="13" t="s">
+      <c r="D101" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E101" s="13" t="s">
+      <c r="E101" s="4" t="s">
         <v>226</v>
       </c>
     </row>
@@ -3933,13 +3881,13 @@
       <c r="B102" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C102" s="14" t="s">
+      <c r="C102" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="D102" s="14" t="s">
+      <c r="D102" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="E102" s="14" t="s">
+      <c r="E102" s="4" t="s">
         <v>228</v>
       </c>
     </row>
@@ -3968,10 +3916,10 @@
       <c r="B105" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C105" s="21" t="s">
+      <c r="C105" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D105" s="21" t="s">
+      <c r="D105" s="2" t="s">
         <v>234</v>
       </c>
     </row>
@@ -3982,7 +3930,7 @@
       <c r="B106" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C106" s="12" t="s">
+      <c r="C106" s="5" t="s">
         <v>237</v>
       </c>
     </row>
@@ -3996,7 +3944,7 @@
       <c r="C107" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D107" s="12" t="s">
+      <c r="D107" s="5" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4007,10 +3955,10 @@
       <c r="B108" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C108" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E108" s="12" t="s">
+      <c r="E108" s="5" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4066,7 +4014,7 @@
       <c r="B114" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C114" s="10" t="s">
+      <c r="C114" s="2" t="s">
         <v>253</v>
       </c>
     </row>
@@ -4080,7 +4028,7 @@
       <c r="C115" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D115" s="10" t="s">
+      <c r="D115" s="2" t="s">
         <v>253</v>
       </c>
     </row>
@@ -4091,10 +4039,10 @@
       <c r="B116" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C116" s="6" t="s">
+      <c r="C116" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E116" s="10" t="s">
+      <c r="E116" s="2" t="s">
         <v>253</v>
       </c>
     </row>
@@ -4141,10 +4089,10 @@
       <c r="B121" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C121" s="19" t="s">
+      <c r="C121" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E121" s="19" t="s">
+      <c r="E121" s="4" t="s">
         <v>267</v>
       </c>
     </row>
@@ -4156,7 +4104,7 @@
         <v>269</v>
       </c>
       <c r="C122" s="2"/>
-      <c r="D122" s="19" t="s">
+      <c r="D122" s="4" t="s">
         <v>267</v>
       </c>
     </row>
@@ -4167,7 +4115,7 @@
       <c r="B123" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C123" s="18" t="s">
+      <c r="C123" s="5" t="s">
         <v>272</v>
       </c>
     </row>
@@ -4179,7 +4127,7 @@
         <v>274</v>
       </c>
       <c r="C124" s="2"/>
-      <c r="D124" s="18" t="s">
+      <c r="D124" s="5" t="s">
         <v>272</v>
       </c>
     </row>
@@ -4226,13 +4174,13 @@
       <c r="B129" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C129" s="18" t="s">
+      <c r="C129" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="D129" s="18" t="s">
+      <c r="D129" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="E129" s="18" t="s">
+      <c r="E129" s="5" t="s">
         <v>284</v>
       </c>
     </row>
@@ -4297,13 +4245,13 @@
       <c r="B136" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C136" s="21" t="s">
+      <c r="C136" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D136" s="21" t="s">
+      <c r="D136" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="E136" s="21" t="s">
+      <c r="E136" s="2" t="s">
         <v>299</v>
       </c>
     </row>
@@ -4332,13 +4280,13 @@
       <c r="B139" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C139" s="21" t="s">
+      <c r="C139" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D139" s="21" t="s">
+      <c r="D139" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="E139" s="21" t="s">
+      <c r="E139" s="2" t="s">
         <v>305</v>
       </c>
     </row>
@@ -4361,10 +4309,10 @@
       <c r="C141" s="2"/>
     </row>
     <row r="142" s="1" customFormat="1" ht="13" spans="1:5">
-      <c r="A142" s="22">
+      <c r="A142" s="7">
         <v>1043</v>
       </c>
-      <c r="B142" s="15" t="s">
+      <c r="B142" s="6" t="s">
         <v>310</v>
       </c>
       <c r="C142" s="4" t="s">
@@ -4372,10 +4320,10 @@
       </c>
     </row>
     <row r="143" s="1" customFormat="1" ht="13" spans="1:5">
-      <c r="A143" s="22">
+      <c r="A143" s="7">
         <v>104301</v>
       </c>
-      <c r="B143" s="15" t="s">
+      <c r="B143" s="6" t="s">
         <v>312</v>
       </c>
       <c r="C143" s="5" t="s">
@@ -4386,13 +4334,13 @@
       </c>
     </row>
     <row r="144" s="1" customFormat="1" ht="13" spans="1:5">
-      <c r="A144" s="22">
+      <c r="A144" s="7">
         <v>104302</v>
       </c>
-      <c r="B144" s="15" t="s">
+      <c r="B144" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="C144" s="6" t="s">
+      <c r="C144" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E144" s="4" t="s">
@@ -4424,13 +4372,13 @@
       <c r="B147" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C147" s="19" t="s">
+      <c r="C147" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="D147" s="19" t="s">
+      <c r="D147" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="E147" s="19" t="s">
+      <c r="E147" s="4" t="s">
         <v>319</v>
       </c>
     </row>
@@ -4450,13 +4398,13 @@
       <c r="B149" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C149" s="7" t="s">
+      <c r="C149" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D149" s="7" t="s">
+      <c r="D149" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="E149" s="7" t="s">
+      <c r="E149" s="2" t="s">
         <v>323</v>
       </c>
     </row>
@@ -4467,13 +4415,13 @@
       <c r="B150" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C150" s="23" t="s">
+      <c r="C150" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="D150" s="23" t="s">
+      <c r="D150" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="E150" s="23" t="s">
+      <c r="E150" s="4" t="s">
         <v>325</v>
       </c>
     </row>
@@ -4484,13 +4432,13 @@
       <c r="B151" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C151" s="7" t="s">
+      <c r="C151" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D151" s="7" t="s">
+      <c r="D151" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="E151" s="7" t="s">
+      <c r="E151" s="2" t="s">
         <v>327</v>
       </c>
     </row>
@@ -4501,13 +4449,13 @@
       <c r="B152" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="C152" s="14" t="s">
+      <c r="C152" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="D152" s="14" t="s">
+      <c r="D152" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="E152" s="14" t="s">
+      <c r="E152" s="4" t="s">
         <v>329</v>
       </c>
     </row>
@@ -4529,13 +4477,13 @@
       <c r="B154" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C154" s="21" t="s">
+      <c r="C154" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D154" s="21" t="s">
+      <c r="D154" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="E154" s="21" t="s">
+      <c r="E154" s="2" t="s">
         <v>333</v>
       </c>
     </row>
@@ -4573,13 +4521,13 @@
       <c r="B158" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C158" s="19" t="s">
+      <c r="C158" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="D158" s="19" t="s">
+      <c r="D158" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="E158" s="19" t="s">
+      <c r="E158" s="4" t="s">
         <v>342</v>
       </c>
     </row>
@@ -4680,13 +4628,13 @@
       <c r="B169" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C169" s="19" t="s">
+      <c r="C169" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="D169" s="19" t="s">
+      <c r="D169" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="E169" s="19" t="s">
+      <c r="E169" s="4" t="s">
         <v>365</v>
       </c>
     </row>
@@ -4708,13 +4656,13 @@
       <c r="B171" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="C171" s="24" t="s">
+      <c r="C171" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="D171" s="24" t="s">
+      <c r="D171" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="E171" s="24" t="s">
+      <c r="E171" s="4" t="s">
         <v>369</v>
       </c>
     </row>
@@ -4725,13 +4673,13 @@
       <c r="B172" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C172" s="23" t="s">
+      <c r="C172" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="D172" s="23" t="s">
+      <c r="D172" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="E172" s="23" t="s">
+      <c r="E172" s="4" t="s">
         <v>371</v>
       </c>
     </row>
@@ -4753,13 +4701,13 @@
       <c r="B174" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C174" s="19" t="s">
+      <c r="C174" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="D174" s="19" t="s">
+      <c r="D174" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="E174" s="19" t="s">
+      <c r="E174" s="4" t="s">
         <v>376</v>
       </c>
     </row>
@@ -4770,13 +4718,13 @@
       <c r="B175" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="C175" s="19" t="s">
+      <c r="C175" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="D175" s="19" t="s">
+      <c r="D175" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="E175" s="19" t="s">
+      <c r="E175" s="4" t="s">
         <v>378</v>
       </c>
     </row>
@@ -4809,13 +4757,13 @@
       <c r="B178" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C178" s="25" t="s">
+      <c r="C178" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="D178" s="25" t="s">
+      <c r="D178" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="E178" s="25" t="s">
+      <c r="E178" s="8" t="s">
         <v>385</v>
       </c>
     </row>
@@ -4837,13 +4785,13 @@
       <c r="B180" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C180" s="21" t="s">
+      <c r="C180" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D180" s="21" t="s">
+      <c r="D180" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="E180" s="21" t="s">
+      <c r="E180" s="2" t="s">
         <v>390</v>
       </c>
     </row>
@@ -4854,13 +4802,13 @@
       <c r="B181" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C181" s="19" t="s">
+      <c r="C181" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="D181" s="19" t="s">
+      <c r="D181" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="E181" s="19" t="s">
+      <c r="E181" s="4" t="s">
         <v>392</v>
       </c>
     </row>
